--- a/static/template_documents/rincian_SPD.xlsx
+++ b/static/template_documents/rincian_SPD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t xml:space="preserve">KOMISI PEMILIHAN UMUM </t>
   </si>
@@ -61,6 +61,9 @@
     <t xml:space="preserve">Terbilang : </t>
   </si>
   <si>
+    <t>{{TERBILANG_TOTAL_DIBAYARKAN}} rupiah</t>
+  </si>
+  <si>
     <t>Kendari,    {{BULAN_TAHUN_SEKARANG}}</t>
   </si>
   <si>
@@ -88,7 +91,7 @@
     <t>NIP. {{NIP_BENDAHARA}}</t>
   </si>
   <si>
-    <t>Nip.{{NIP_SEKRETARIS}}</t>
+    <t>NIP. {{NIP_SEKRETARIS}}</t>
   </si>
   <si>
     <t>PERHITUNGAN SPD RAMPUNG</t>
@@ -120,7 +123,7 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="59" formatCode="&quot; Rp&quot;* #,##0&quot; &quot;;&quot; Rp&quot;* (#,##0);&quot; Rp&quot;* &quot;- &quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -178,13 +181,6 @@
     </font>
     <font>
       <b val="1"/>
-      <i val="1"/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b val="1"/>
       <u val="single"/>
       <sz val="12"/>
       <color indexed="8"/>
@@ -223,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -416,21 +412,6 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom>
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -460,21 +441,6 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top>
-        <color indexed="8"/>
-      </top>
-      <bottom>
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="8"/>
@@ -498,21 +464,6 @@
         <color indexed="8"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top>
-        <color indexed="8"/>
-      </top>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
@@ -601,7 +552,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -720,39 +671,30 @@
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -764,17 +706,20 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
@@ -794,58 +739,58 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="21" fontId="10" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="21" fontId="11" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -2151,187 +2096,187 @@
       <c r="E12" s="36"/>
       <c r="F12" s="37"/>
       <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
+      <c r="H12" s="38"/>
       <c r="I12" s="32"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="33"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
       <c r="I13" s="32"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="33"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
       <c r="I14" s="32"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="33"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="32"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="33"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
       <c r="I16" s="32"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="33"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="32"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="33"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="44"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="32"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="33"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="44"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="32"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="33"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="32"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="33"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="44"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="32"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="33"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="32"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="33"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="44"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
       <c r="I23" s="32"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="33"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="33"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="33"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="33"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
       <c r="I27" s="32"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="33"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="50"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
       <c r="I28" s="32"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="51"/>
+      <c r="A29" s="48"/>
       <c r="B29" t="s" s="30">
         <v>13</v>
       </c>
@@ -2339,34 +2284,36 @@
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
-      <c r="G29" t="s" s="52">
+      <c r="G29" t="s" s="49">
         <v>14</v>
       </c>
-      <c r="H29" s="53"/>
+      <c r="H29" s="50"/>
       <c r="I29" s="32"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="51"/>
-      <c r="B30" t="s" s="54">
+      <c r="A30" s="48"/>
+      <c r="B30" t="s" s="51">
         <v>15</v>
       </c>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="57"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" t="s" s="53">
+        <v>16</v>
+      </c>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
       <c r="I30" s="32"/>
     </row>
     <row r="31" ht="9" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
       <c r="I31" s="18"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -2377,7 +2324,7 @@
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" t="s" s="22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" s="23"/>
       <c r="I32" s="18"/>
@@ -2385,29 +2332,29 @@
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="21"/>
       <c r="B33" t="s" s="25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" t="s" s="25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H33" s="24"/>
       <c r="I33" s="18"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="21"/>
-      <c r="B34" t="s" s="59">
-        <v>19</v>
-      </c>
-      <c r="C34" s="60"/>
+      <c r="B34" t="s" s="57">
+        <v>20</v>
+      </c>
+      <c r="C34" s="58"/>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
-      <c r="G34" t="s" s="61">
-        <v>19</v>
+      <c r="G34" t="s" s="59">
+        <v>20</v>
       </c>
       <c r="H34" s="24"/>
       <c r="I34" s="18"/>
@@ -2426,17 +2373,17 @@
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="21"/>
       <c r="B36" t="s" s="26">
-        <v>20</v>
-      </c>
-      <c r="C36" s="62"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
+        <v>21</v>
+      </c>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
       <c r="F36" s="24"/>
       <c r="G36" t="s" s="26">
-        <v>21</v>
-      </c>
-      <c r="H36" s="62"/>
-      <c r="I36" s="63"/>
+        <v>22</v>
+      </c>
+      <c r="H36" s="60"/>
+      <c r="I36" s="61"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="21"/>
@@ -2473,56 +2420,56 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21"/>
-      <c r="B40" t="s" s="64">
-        <v>22</v>
-      </c>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
+      <c r="B40" t="s" s="62">
+        <v>23</v>
+      </c>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
       <c r="F40" s="24"/>
-      <c r="G40" t="s" s="64">
-        <v>23</v>
-      </c>
-      <c r="H40" s="66"/>
-      <c r="I40" s="67"/>
+      <c r="G40" t="s" s="62">
+        <v>24</v>
+      </c>
+      <c r="H40" s="64"/>
+      <c r="I40" s="65"/>
     </row>
     <row r="41" ht="16.5" customHeight="1">
       <c r="A41" s="21"/>
-      <c r="B41" t="s" s="68">
-        <v>24</v>
-      </c>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="70"/>
-      <c r="G41" t="s" s="71">
+      <c r="B41" t="s" s="66">
         <v>25</v>
       </c>
-      <c r="H41" s="72"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="68"/>
+      <c r="G41" t="s" s="69">
+        <v>26</v>
+      </c>
+      <c r="H41" s="70"/>
       <c r="I41" s="18"/>
     </row>
     <row r="42" ht="8" customHeight="1">
       <c r="A42" s="21"/>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
       <c r="I42" s="18"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="21"/>
-      <c r="B43" t="s" s="74">
-        <v>26</v>
-      </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
+      <c r="B43" t="s" s="72">
+        <v>27</v>
+      </c>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="73"/>
       <c r="I43" s="18"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -2540,13 +2487,13 @@
       <c r="A45" s="21"/>
       <c r="B45" s="24"/>
       <c r="C45" t="s" s="25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
-      <c r="G45" t="s" s="61">
-        <v>19</v>
+      <c r="G45" t="s" s="59">
+        <v>20</v>
       </c>
       <c r="H45" s="24"/>
       <c r="I45" s="18"/>
@@ -2555,13 +2502,13 @@
       <c r="A46" s="21"/>
       <c r="B46" s="24"/>
       <c r="C46" t="s" s="25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
-      <c r="G46" t="s" s="61">
-        <v>19</v>
+      <c r="G46" t="s" s="59">
+        <v>20</v>
       </c>
       <c r="H46" s="24"/>
       <c r="I46" s="18"/>
@@ -2570,12 +2517,12 @@
       <c r="A47" s="21"/>
       <c r="B47" s="24"/>
       <c r="C47" t="s" s="25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="24"/>
       <c r="F47" s="24"/>
-      <c r="G47" s="76">
+      <c r="G47" s="74">
         <v>0</v>
       </c>
       <c r="H47" s="24"/>
@@ -2600,9 +2547,9 @@
       <c r="E49" s="24"/>
       <c r="F49" s="24"/>
       <c r="G49" t="s" s="26">
-        <v>30</v>
-      </c>
-      <c r="H49" s="62"/>
+        <v>31</v>
+      </c>
+      <c r="H49" s="60"/>
       <c r="I49" s="18"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -2645,10 +2592,10 @@
       <c r="D53" s="24"/>
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
-      <c r="G53" t="s" s="64">
-        <v>31</v>
-      </c>
-      <c r="H53" s="65"/>
+      <c r="G53" t="s" s="62">
+        <v>32</v>
+      </c>
+      <c r="H53" s="63"/>
       <c r="I53" s="18"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
@@ -2658,22 +2605,22 @@
       <c r="D54" s="24"/>
       <c r="E54" s="24"/>
       <c r="F54" s="24"/>
-      <c r="G54" t="s" s="77">
-        <v>32</v>
-      </c>
-      <c r="H54" s="78"/>
+      <c r="G54" t="s" s="75">
+        <v>33</v>
+      </c>
+      <c r="H54" s="76"/>
       <c r="I54" s="18"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="79"/>
-      <c r="B55" s="80"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="80"/>
-      <c r="F55" s="80"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="80"/>
-      <c r="I55" s="81"/>
+      <c r="A55" s="77"/>
+      <c r="B55" s="78"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="78"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="78"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="78"/>
+      <c r="I55" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -2692,7 +2639,6 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F30:H30"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B4:I4"/>
@@ -2716,6 +2662,7 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C26:F26"/>
+    <mergeCell ref="E30:H30"/>
   </mergeCells>
   <pageMargins left="0.62" right="0.393701" top="0.748031" bottom="0.748031" header="0.314961" footer="0.314961"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="89" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/static/template_documents/rincian_SPD.xlsx
+++ b/static/template_documents/rincian_SPD.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Jumlah </t>
   </si>
   <si>
-    <t>{{TOTAL_BIAYA}}</t>
+    <t>Rp {{TOTAL_BIAYA}}</t>
   </si>
   <si>
     <t xml:space="preserve">Terbilang : </t>
@@ -552,7 +552,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -668,6 +668,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -680,6 +683,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -695,13 +701,16 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
@@ -733,50 +742,32 @@
     <xf numFmtId="49" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="59" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="21" fontId="10" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -2096,187 +2087,187 @@
       <c r="E12" s="36"/>
       <c r="F12" s="37"/>
       <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="39"/>
       <c r="I12" s="32"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="33"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="32"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="33"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="32"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="33"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="32"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="33"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="32"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="33"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="32"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="33"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
       <c r="I18" s="32"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="33"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="32"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="33"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="32"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="33"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="32"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="33"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
       <c r="I22" s="32"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="33"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="41"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
       <c r="I23" s="32"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="33"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="33"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="33"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="33"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="32"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="33"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="50"/>
       <c r="I28" s="32"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="48"/>
+      <c r="A29" s="51"/>
       <c r="B29" t="s" s="30">
         <v>13</v>
       </c>
@@ -2284,36 +2275,36 @@
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
-      <c r="G29" t="s" s="49">
+      <c r="G29" t="s" s="52">
         <v>14</v>
       </c>
-      <c r="H29" s="50"/>
+      <c r="H29" s="53"/>
       <c r="I29" s="32"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="48"/>
-      <c r="B30" t="s" s="51">
+      <c r="A30" s="51"/>
+      <c r="B30" t="s" s="54">
         <v>15</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" t="s" s="53">
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" t="s" s="56">
         <v>16</v>
       </c>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="55"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="58"/>
       <c r="I30" s="32"/>
     </row>
     <row r="31" ht="9" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
       <c r="I31" s="18"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -2346,14 +2337,14 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="21"/>
-      <c r="B34" t="s" s="57">
+      <c r="B34" t="s" s="60">
         <v>20</v>
       </c>
-      <c r="C34" s="58"/>
+      <c r="C34" s="61"/>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
-      <c r="G34" t="s" s="59">
+      <c r="G34" t="s" s="62">
         <v>20</v>
       </c>
       <c r="H34" s="24"/>
@@ -2375,15 +2366,15 @@
       <c r="B36" t="s" s="26">
         <v>21</v>
       </c>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="24"/>
-      <c r="G36" t="s" s="26">
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" t="s" s="26">
         <v>22</v>
       </c>
-      <c r="H36" s="60"/>
-      <c r="I36" s="61"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="18"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="21"/>
@@ -2420,56 +2411,56 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21"/>
-      <c r="B40" t="s" s="62">
+      <c r="B40" t="s" s="63">
         <v>23</v>
       </c>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="24"/>
-      <c r="G40" t="s" s="62">
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" t="s" s="63">
         <v>24</v>
       </c>
-      <c r="H40" s="64"/>
-      <c r="I40" s="65"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="18"/>
     </row>
     <row r="41" ht="16.5" customHeight="1">
       <c r="A41" s="21"/>
-      <c r="B41" t="s" s="66">
+      <c r="B41" t="s" s="64">
         <v>25</v>
       </c>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="68"/>
-      <c r="G41" t="s" s="69">
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" t="s" s="64">
         <v>26</v>
       </c>
-      <c r="H41" s="70"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
       <c r="I41" s="18"/>
     </row>
     <row r="42" ht="8" customHeight="1">
       <c r="A42" s="21"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
       <c r="I42" s="18"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="21"/>
-      <c r="B43" t="s" s="72">
+      <c r="B43" t="s" s="67">
         <v>27</v>
       </c>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
+      <c r="H43" s="68"/>
       <c r="I43" s="18"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -2492,7 +2483,7 @@
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
-      <c r="G45" t="s" s="59">
+      <c r="G45" t="s" s="62">
         <v>20</v>
       </c>
       <c r="H45" s="24"/>
@@ -2507,7 +2498,7 @@
       <c r="D46" s="24"/>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
-      <c r="G46" t="s" s="59">
+      <c r="G46" t="s" s="62">
         <v>20</v>
       </c>
       <c r="H46" s="24"/>
@@ -2522,7 +2513,7 @@
       <c r="D47" s="24"/>
       <c r="E47" s="24"/>
       <c r="F47" s="24"/>
-      <c r="G47" s="74">
+      <c r="G47" s="69">
         <v>0</v>
       </c>
       <c r="H47" s="24"/>
@@ -2549,7 +2540,7 @@
       <c r="G49" t="s" s="26">
         <v>31</v>
       </c>
-      <c r="H49" s="60"/>
+      <c r="H49" s="70"/>
       <c r="I49" s="18"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -2592,10 +2583,10 @@
       <c r="D53" s="24"/>
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
-      <c r="G53" t="s" s="62">
+      <c r="G53" t="s" s="63">
         <v>32</v>
       </c>
-      <c r="H53" s="63"/>
+      <c r="H53" s="71"/>
       <c r="I53" s="18"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
@@ -2605,37 +2596,31 @@
       <c r="D54" s="24"/>
       <c r="E54" s="24"/>
       <c r="F54" s="24"/>
-      <c r="G54" t="s" s="75">
+      <c r="G54" t="s" s="72">
         <v>33</v>
       </c>
-      <c r="H54" s="76"/>
+      <c r="H54" s="73"/>
       <c r="I54" s="18"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="77"/>
-      <c r="B55" s="78"/>
-      <c r="C55" s="78"/>
-      <c r="D55" s="78"/>
-      <c r="E55" s="78"/>
-      <c r="F55" s="78"/>
-      <c r="G55" s="78"/>
-      <c r="H55" s="78"/>
-      <c r="I55" s="79"/>
+      <c r="A55" s="74"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="75"/>
+      <c r="D55" s="75"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="75"/>
+      <c r="H55" s="75"/>
+      <c r="I55" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="G41:H41"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="G49:H49"/>
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="G54:H54"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G40:H40"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B30:D30"/>
@@ -2663,6 +2648,12 @@
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="E30:H30"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="B36:E36"/>
   </mergeCells>
   <pageMargins left="0.62" right="0.393701" top="0.748031" bottom="0.748031" header="0.314961" footer="0.314961"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="89" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
